--- a/results/Int Task Remove ACC 0.3/Rando_8_permute.xlsx
+++ b/results/Int Task Remove ACC 0.3/Rando_8_permute.xlsx
@@ -440,797 +440,797 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7067017350074476</v>
+        <v>0.7120852531447573</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7109166302980681</v>
+        <v>0.7020739112915165</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7099034590721309</v>
+        <v>0.6945703935146743</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.703515137705032</v>
+        <v>0.6774501170875769</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.707378899003436</v>
+        <v>0.6849536348644192</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7049496053524278</v>
+        <v>0.6787291331142207</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7061517001837097</v>
+        <v>0.6764369458616397</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.7276255875298834</v>
+        <v>0.6764369458616397</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.72208822700185</v>
+        <v>0.6984508908053746</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.7256777755033994</v>
+        <v>0.6987685528129985</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.7220714910095537</v>
+        <v>0.7043158905672086</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.718112463293463</v>
+        <v>0.7034314577435505</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.7151598480371899</v>
+        <v>0.707913807064906</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.6763448979040101</v>
+        <v>0.7084203926778747</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.6781304995436224</v>
+        <v>0.6956353819475288</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.6406582909462144</v>
+        <v>0.6851860076805331</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.6291790094609853</v>
+        <v>0.640374100923183</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.6329072735909904</v>
+        <v>0.641455825348334</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.5886569881135834</v>
+        <v>0.6237938820936469</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.5886569881135834</v>
+        <v>0.6271510577790823</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.5856776596388373</v>
+        <v>0.6284818910126434</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.5404862964407694</v>
+        <v>0.6371791356246195</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.5396620488201769</v>
+        <v>0.645413243834396</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.5304466321390272</v>
+        <v>0.6354186379734515</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.5132310892942432</v>
+        <v>0.63801175124136</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.5132310892942432</v>
+        <v>0.6574425601433631</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.5151370613399865</v>
+        <v>0.6269270529591165</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.5148110313362145</v>
+        <v>0.6181445191556305</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.5380856470842683</v>
+        <v>0.6122978646161213</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.5378465155020348</v>
+        <v>0.6122978646161213</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.5457278804895664</v>
+        <v>0.6045301112686011</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.5355543282494538</v>
+        <v>0.6120001570608508</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.5262384956145263</v>
+        <v>0.6179536644742516</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.5114171652061295</v>
+        <v>0.597716953173981</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.5087471307428593</v>
+        <v>0.5854401372866322</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.4915415651242518</v>
+        <v>0.5815779852182567</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.4890086370594089</v>
+        <v>0.5799713299578124</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.4958333816102342</v>
+        <v>0.5788294203295961</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.4922103611240922</v>
+        <v>0.5788294203295961</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.4998860665139829</v>
+        <v>0.581800380808194</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.4998860665139829</v>
+        <v>0.592060831469845</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.4960824904186444</v>
+        <v>0.5803559359346215</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.4948218196143255</v>
+        <v>0.5520038776006766</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.5033385086171049</v>
+        <v>0.5367779867631175</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.5079998043176286</v>
+        <v>0.5381857411920403</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.5153578476998953</v>
+        <v>0.5443516669692019</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.5201813537872907</v>
+        <v>0.561311342239456</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.5207130433887037</v>
+        <v>0.5660778815838428</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.5554267098712745</v>
+        <v>0.5421495965982164</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.5647943597131193</v>
+        <v>0.5699146078177683</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.5659629825598086</v>
+        <v>0.5518146321493262</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.5738543247735169</v>
+        <v>0.528864437175016</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.5700890483528565</v>
+        <v>0.5276188931329648</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.5743840832988958</v>
+        <v>0.505011464154723</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.5678419195410733</v>
+        <v>0.5382452827030945</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.5331749207293288</v>
+        <v>0.540606023154889</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.5172332443750973</v>
+        <v>0.5569422827121062</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.5146066591225963</v>
+        <v>0.5578167383095876</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.5146066591225963</v>
+        <v>0.5632739591822022</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.4956071238682285</v>
+        <v>0.5475498507278225</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.4845758520229309</v>
+        <v>0.5459615406897032</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.4885165345166967</v>
+        <v>0.5339924095838016</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.4880920196351811</v>
+        <v>0.5273717154005888</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.4994592987104274</v>
+        <v>0.524788579358857</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.4994592987104274</v>
+        <v>0.5435840642456122</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.5009407558746551</v>
+        <v>0.5205237979373534</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.4994209990357494</v>
+        <v>0.5190207770907438</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.5199602455813762</v>
+        <v>0.5204117955273704</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.5165947018997926</v>
+        <v>0.5415242498091453</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.5161048522791203</v>
+        <v>0.5291338222817852</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.5026629538511449</v>
+        <v>0.5316651411165997</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.5147672602794395</v>
+        <v>0.5325495739402577</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.5128963694483173</v>
+        <v>0.5224545521255354</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.5128963694483173</v>
+        <v>0.5060616476713153</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.5281859857950048</v>
+        <v>0.5053661384530022</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.5271293653582982</v>
+        <v>0.5059496452613326</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.5117647588922832</v>
+        <v>0.4997402702734017</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.5059029775905063</v>
+        <v>0.4997402702734017</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.4836299466121846</v>
+        <v>0.4997402702734017</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.4880923414811869</v>
+        <v>0.5034601664072588</v>
       </c>
     </row>
     <row r="82">
@@ -1240,87 +1240,87 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.4880923414811869</v>
+        <v>0.5034601664072588</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.4880923414811869</v>
+        <v>0.5034601664072588</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.4894180251786567</v>
+        <v>0.5196071805131255</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.5148963205277245</v>
+        <v>0.484741924561871</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.5097702791949731</v>
+        <v>0.4864071557953523</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.512570661290551</v>
+        <v>0.4881493082241954</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.5161685777882485</v>
+        <v>0.4852887409255519</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.5191311702706982</v>
+        <v>0.4918074099249584</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.4994850463908833</v>
+        <v>0.4918074099249584</v>
       </c>
     </row>
   </sheetData>
